--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9279a9906ec44a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6553fd1a615a41e0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6553fd1a615a41e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f64d7df2ed84388"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f64d7df2ed84388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6eca5e9cde6145c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6eca5e9cde6145c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3d94a8ff568431c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3d94a8ff568431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R935af9cb695f4017"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R935af9cb695f4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc26ffc7ccf7d4025"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc26ffc7ccf7d4025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R046cb4d5b1ff45af"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R046cb4d5b1ff45af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cc11cdcc0324bdd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cc11cdcc0324bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a782d244f2e4638"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a782d244f2e4638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3be4be5974894725"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3be4be5974894725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24965ed2b6014011"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24965ed2b6014011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9f6fd6189cd49f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9f6fd6189cd49f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21060da151c3444a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21060da151c3444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref6fbc59762c46bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref6fbc59762c46bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb338c8ad7cd44502"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb338c8ad7cd44502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd071b3521ed8423d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd071b3521ed8423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R713f62aab9ab4d51"/>
   </x:sheets>
 </x:workbook>
 </file>
